--- a/outputs/reports/candidate_results.xlsx
+++ b/outputs/reports/candidate_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,157 +456,769 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Experience</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Similarity Score</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Certifications</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Semantic Similarity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Rerank Score</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Skill Match</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Experience Match</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Education Match</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ATS Score</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Suitable Role</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Weaknesses</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Missing Skills</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Noah Clark</t>
+          <t>CHINMAYEE RAMINI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>noah.clark@example.com</t>
+          <t>chinmayeeramini@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+1-555-0102</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>+91 7658920223</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jangaon, Telangana, India</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Python, Pandas, scikit-learn, SQL, Power BI</t>
+          <t>['Python', 'MySQL', 'Supervised Learning', 'Unsupervised Learning', 'Predictive Modeling', 'Model Training', 'Model Evaluation', 'DataPreprocessing', 'DataAnalysis', 'StatisticalAnalysis', 'DataVisualization', 'FeatureEngineering', 'LLMs', 'Generative AI', 'Prompt Engineering', 'Agentic AI', 'Embeddings', 'Semantic Search', 'RAG', 'NLP', 'NumPy', 'Pandas', 'Scikit-learn', 'Matplotlib', 'Seaborn', 'PyTorch', 'Git', 'GitHub', 'Jupyter', 'n8n', 'Sentence Transformers', 'FAISS']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Data Scientist with experience building scalable software solutions and collaborating in Agile teams.</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0.658</v>
+          <t>['Bachelor of Technology (B.Tech), Computer Science, Rajiv Gandhi University of Knowledge Technologies (RGUKT), Basar, 2023–2027 (Expected), CGPA: 9.1', 'Pre-University Course (PUC), Rajiv Gandhi University of Knowledge Technologies (RGUKT), Basar, 2021–2023, CGPA: 9.74', 'Secondary School Certificate (SSC), Ekashila Public School, Jangaon, 2021, CGPA: 10.0']</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Data Science Intern at Mue.AI Pvt Ltd, developed an AI-powered social media automation platform using n8n, REST APIs, JSON, Groq Llama, Whisper, Google Drive, Cloudinary, and CloudConvert; automated publishing to LinkedIn, YouTube, and Instagram with SEO‑optimized titles, captions, hashtags, and metadata.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>['Agentic RAG Policy Assistant - Python, RAG, LLMs, Groq, Render', 'AI-Powered Recruitment Automation System - Python, Streamlit, LLMs, RAG, FAISS, SentenceTransformers', 'Customer Churn Prediction - Python, Scikit-learn, XGBoost, LightGBM, CatBoost, SHAP']</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>['Artificial Intelligence Fundamentals – IBM SkillsBuild', 'Machine Learning for Business Analytics – The Wharton School', 'Data Science &amp; Machine Learning – Gilbert Research Center', 'Python Course – Geeks for Geeks', 'Data Science – Thiranex']</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-4.677</v>
+      </c>
+      <c r="L2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Consider</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>GenAI Analyst</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Strong Python programming skills, Hands‑on experience with Generative AI, LLMs, RAG and Prompt Engineering, Relevant internship building AI‑powered automation platform, Projects demonstrating end‑to‑end AI solutions (policy assistant, recruitment automation, churn prediction), Solid foundation in Machine Learning and model evaluation (XGBoost, SHAP), Good academic record (CGPA 9.1), Familiarity with data preprocessing, analysis and visualization using Python libraries</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>No explicit experience with Tableau or Power BI for data visualization, Limited exposure to cloud platforms such as AWS or Google Cloud for data engineering, No demonstrated design of large‑scale data pipelines or use of orchestration tools (e.g., Airflow), No mention of production‑grade deployment practices beyond Render</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Tableau, Power BI, AWS or Google Cloud services, Data pipeline orchestration (Airflow, Prefect, etc.), Big‑data processing frameworks (Spark, Hadoop)</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sophia Miller</t>
+          <t>Emma Wilson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sophia.miller@example.com</t>
+          <t>emma.wilson@example.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+1-555-0105</t>
+          <t>+1-555-0101</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>React, JavaScript, HTML, CSS, Redux</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>-2.381976426469702e+38</v>
+          <t>['Python', 'FastAPI', 'SQL', 'Docker', 'Git']</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>['B.Tech in Computer Science, GPA: 8.8/10']</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Python Developer with experience building scalable software solutions and collaborating in Agile teams.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>['Built REST APIs', 'Inventory System']</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-9.175000000000001</v>
+      </c>
+      <c r="L3" t="n">
+        <v>40</v>
+      </c>
+      <c r="M3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O3" t="n">
+        <v>32</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Consider</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>GenAI Analyst</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Python programming, Strong GPA (8.8), Experience building REST APIs, SQL knowledge, Docker and Git familiarity</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>No experience with Generative AI, Machine Learning, or NLP, Lacks data visualization tools (Tableau, Power BI), No cloud platform experience (AWS, GCP), No data engineering or pipeline experience, Limited exposure to analytics and client-facing reporting</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Generative AI, Machine Learning, Natural Language Processing, Data Visualization (Tableau, Power BI), Data Engineering and pipeline design, Cloud platforms (AWS, Google Cloud), Advanced analytics techniques, Domain knowledge in pharmaceutical/CPG industries</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Olivia Brown</t>
+          <t>Noah Clark</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>olivia.brown@example.com</t>
+          <t>noah.clark@example.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+1-555-0103</t>
+          <t>+1-555-0102</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PyTorch, TensorFlow, Transformers, FAISS, RAG</t>
+          <t>['Python', 'Pandas', 'scikit-learn', 'SQL', 'Power BI']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ML Engineer with experience building scalable software solutions and collaborating in Agile teams.</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.301</v>
+          <t>['B.Tech in Computer Science, GPA: 8.8/10']</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Data Scientist with experience building scalable software solutions and collaborating in Agile teams.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>['Customer Churn', 'Sales Forecast']</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-8.996</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N4" t="n">
+        <v>100</v>
+      </c>
+      <c r="O4" t="n">
+        <v>32</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Consider</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>GenAI Analyst</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Python programming, Machine Learning with scikit-learn, Power BI data visualization, B.Tech Computer Science with 8.8 GPA</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>No experience with Generative AI, No NLP experience, No data engineering or cloud platform experience, Limited project scope to churn and forecasting</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Generative AI, Natural Language Processing (NLP), Tableau, AWS or Google Cloud, Data pipeline design and implementation, Data integration and management, Advanced analytics techniques</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ethan Johnson</t>
+          <t>Olivia Brown</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ethan.johnson@example.com</t>
+          <t>olivia.brown@example.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1-555-0106</t>
+          <t>+1-555-0103</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Docker, Kubernetes, Jenkins, Linux</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>0.259</v>
+          <t>['PyTorch', 'TensorFlow', 'Transformers', 'FAISS', 'RAG']</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>['B.Tech in Computer Science, GPA: 8.8/10']</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ML Engineer with experience building scalable software solutions and collaborating in Agile teams.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>['Resume Screening AI', 'Chatbot']</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-8.968999999999999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>20</v>
+      </c>
+      <c r="M5" t="n">
+        <v>50</v>
+      </c>
+      <c r="N5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O5" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Consider</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>GenAI Analyst</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>B.Tech Computer Science with GPA 8.8/10, Experience with PyTorch and TensorFlow, Knowledge of Transformers and Retrieval‑Augmented Generation (RAG), ML engineering background</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>No explicit mention of Python programming proficiency, Limited evidence of NLP project experience, No data visualization tool experience (Tableau/Power BI), No cloud platform (AWS/GCP) or data pipeline experience, No demonstrated client‑facing or communication skills</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Python programming, NLP techniques beyond Transformers, Data visualization (Tableau, Power BI), Data pipeline creation and data engineering, Cloud platforms (AWS, Google Cloud), Client‑focused analysis and presentation, Cross‑functional collaboration experience</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liam Davis</t>
+          <t>Ethan Johnson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>liam.davis@example.com</t>
+          <t>ethan.johnson@example.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1-555-0104</t>
+          <t>+1-555-0106</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Java, Spring Boot, MySQL, Kafka, Docker</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>0.298</v>
-      </c>
+          <t>['AWS', 'Docker', 'Kubernetes', 'Jenkins', 'Linux']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>['B.Tech in Computer Science, GPA: 8.8/10']</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DevOps Engineer with experience building scalable software solutions and collaborating in Agile teams.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>['CI/CD', 'K8s Migration']</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-9.151999999999999</v>
+      </c>
+      <c r="L6" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" t="n">
+        <v>50</v>
+      </c>
+      <c r="N6" t="n">
+        <v>100</v>
+      </c>
+      <c r="O6" t="n">
+        <v>26</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>AWS, Docker, Kubernetes, Jenkins, Linux, CI/CD project experience</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>No Python experience, No Generative AI or ML knowledge, No NLP experience, No data analysis or visualization skills, Lacks experience with Tableau/Power BI</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Python programming, Generative AI, Machine Learning, Natural Language Processing, Data analysis, Data visualization (Tableau, Power BI), AI/ML model development, Advanced analytics, Data pipeline creation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sophia Miller</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sophia.miller@example.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>+1-555-0105</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>['React', 'JavaScript', 'HTML', 'CSS', 'Redux']</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>['B.Tech in Computer Science, GPA: 8.8/10']</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Frontend Developer with experience building scalable software solutions and collaborating in Agile teams.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>['E-commerce UI', 'Dashboard']</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-8.923</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50</v>
+      </c>
+      <c r="N7" t="n">
+        <v>100</v>
+      </c>
+      <c r="O7" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Not evaluated by LLM</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Liam Davis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>liam.davis@example.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>+1-555-0104</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>['Java', 'Spring Boot', 'MySQL', 'Kafka', 'Docker']</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>['B.Tech in Computer Science, GPA: 8.8/10']</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Java Backend Developer with experience building scalable software solutions and collaborating in Agile teams.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>['Banking API', 'Order Service']</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-9.167</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>100</v>
+      </c>
+      <c r="O8" t="n">
+        <v>20</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Not evaluated by LLM</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>j.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-8.063000000000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Not evaluated by LLM</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Job_Description.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-8.063000000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
+        <v>50</v>
+      </c>
+      <c r="O10" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Not evaluated by LLM</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
